--- a/project/HW6/22127310/22127310_TestCases.xlsx
+++ b/project/HW6/22127310/22127310_TestCases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thanhthuy/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thanhthuy/Documents/Testing-PRJ-SM/project/HW6/22127310/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14156E7E-217E-FE42-AF80-29E02CE8A029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E8CA94-5401-1C46-A1E4-5A774C9FECB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="440" yWindow="760" windowWidth="29400" windowHeight="18360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="2" r:id="rId1"/>
@@ -163,9 +163,6 @@
     <t>Feature ID</t>
   </si>
   <si>
-    <t>Feature 01: User Sign In</t>
-  </si>
-  <si>
     <t xml:space="preserve">Homepage → Category → Product  </t>
   </si>
   <si>
@@ -286,6 +283,9 @@
   </si>
   <si>
     <t>Cao Uyen Nhi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feature 01: Homepage → Category → Product  </t>
   </si>
 </sst>
 </file>
@@ -357,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -382,23 +382,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -962,10 +946,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1038,7 +1022,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1060,28 +1044,28 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" t="s">
-        <v>31</v>
-      </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K3" s="7">
         <v>45880</v>
@@ -1096,28 +1080,28 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="F4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" t="s">
         <v>36</v>
       </c>
-      <c r="G4" t="s">
-        <v>37</v>
-      </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K4" s="7">
         <v>45880</v>
@@ -1132,28 +1116,28 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K5" s="7">
         <v>45880</v>
@@ -1168,28 +1152,28 @@
         <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K6" s="7">
         <v>45880</v>
@@ -1204,28 +1188,28 @@
         <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K7" s="7">
         <v>45880</v>
@@ -1240,28 +1224,28 @@
         <v>22</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="F8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K8" s="7">
         <v>45880</v>
@@ -1276,28 +1260,28 @@
         <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K9" s="7">
         <v>45880</v>
@@ -1312,28 +1296,28 @@
         <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K10" s="7">
         <v>45880</v>
@@ -1341,312 +1325,206 @@
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="13"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="16"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="16"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="13"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="13"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="13"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="13"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="13"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="K18" s="7"/>
     </row>
     <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="13"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="13"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="13"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="K21" s="7"/>
     </row>
     <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="13"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="K22" s="7"/>
     </row>
     <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="13"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="K23" s="7"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="15"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
+      <c r="B24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="13"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="13"/>
+      <c r="A25" s="2"/>
+      <c r="B25" s="6"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="13"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="13"/>
+      <c r="A26" s="2"/>
+      <c r="B26" s="6"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="13"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="13"/>
+      <c r="A27" s="2"/>
+      <c r="B27" s="6"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="2"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="13"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="13"/>
+      <c r="A28" s="2"/>
+      <c r="B28" s="6"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="2"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="13"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="13"/>
+      <c r="A29" s="2"/>
+      <c r="B29" s="6"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="2"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="13"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="13"/>
+      <c r="A30" s="2"/>
+      <c r="B30" s="6"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="2"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="13"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="13"/>
+      <c r="A31" s="2"/>
+      <c r="B31" s="6"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="2"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="13"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="13"/>
+      <c r="A32" s="2"/>
+      <c r="B32" s="6"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="2"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
